--- a/others/houseprice_name.xlsx
+++ b/others/houseprice_name.xlsx
@@ -1,29 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unisydneyedu-my.sharepoint.com/personal/cyeh0303_uni_sydney_edu_au/Documents/Desktop/R Transportation/R Github Project/NYCU_TDX/others/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{30F4843C-3527-4293-AD32-7513A57F9807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A612458C-274C-424E-91F5-7E02A441F92A}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="8_{30F4843C-3527-4293-AD32-7513A57F9807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EB3DB32-D729-4699-B445-1F550601B618}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="houseprice_name" sheetId="1" r:id="rId1"/>
+    <sheet name="不動產買賣" sheetId="1" r:id="rId1"/>
+    <sheet name="預售屋買賣" sheetId="3" r:id="rId2"/>
+    <sheet name="不動產租賃" sheetId="2" r:id="rId3"/>
+    <sheet name="停車場買賣" sheetId="5" r:id="rId4"/>
+    <sheet name="建物不動產買賣" sheetId="6" r:id="rId5"/>
+    <sheet name="土地不動產買賣" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">houseprice_name!$A$1:$B$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">土地不動產買賣!$A$1:$B$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">不動產租賃!$A$1:$B$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">不動產買賣!$A$1:$B$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">建物不動產買賣!$A$1:$B$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">停車場買賣!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="123">
   <si>
     <t>TOWNNAME</t>
   </si>
@@ -139,22 +148,6 @@
     <t>RENT_LEVEL</t>
   </si>
   <si>
-    <t>欄位名稱</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>鄉鎮市區</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -332,54 +325,6 @@
         <charset val="136"/>
       </rPr>
       <t>建物移轉總面積平方公尺</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>建物現況格局房</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>建物現況格局廳</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>建物現況格局衛</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>建物現況格局隔間</t>
     </r>
   </si>
   <si>
@@ -649,8 +594,508 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>COUNTYNAME</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>欄位名稱</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>縣市</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>鄉鎮市區</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建物現況格局</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>房</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建物現況格局</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>廳</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建物現況格局</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>衛</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建物現況格局</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>隔間</t>
+    </r>
+  </si>
+  <si>
     <t>FURNITURE</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PARKING_UNIT_PRICE</t>
+  </si>
+  <si>
+    <t>RENT_TYPE</t>
+  </si>
+  <si>
+    <t>CONCIERGE</t>
+  </si>
+  <si>
+    <t>RENT_PERIOD</t>
+  </si>
+  <si>
+    <t>EQUIPMENT</t>
+  </si>
+  <si>
+    <t>RENT_SERVICE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>總額元</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>車位面積平方公尺</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>車位總額元</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>出租型態</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>有無管理員</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>租賃期間</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>有無電梯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>附屬設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>租賃住宅服務</t>
+    </r>
+  </si>
+  <si>
+    <t>CONTRACT_TERMINATE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>解約情形</t>
+    </r>
+  </si>
+  <si>
+    <t>PARKING_FLOOR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>車位價格</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>車位所在樓層</t>
+    </r>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>LAYER</t>
+  </si>
+  <si>
+    <t>TRANSFER</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>屋齡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建物移轉面積平方公尺</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建築完成日期</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>總層數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建物分層</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>移轉情形</t>
+    </r>
+  </si>
+  <si>
+    <t>DISTRICT_NUM</t>
+  </si>
+  <si>
+    <t>RIGHTS_HOLDER_ALL</t>
+  </si>
+  <si>
+    <t>RIGHTS_HOLDER</t>
+  </si>
+  <si>
+    <t>LAND_SERIAL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>土地位置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>土地移轉面積平方公尺</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>使用分區或編定</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>權利人持分分母</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>權利人持分分子</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>地號</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1378,10 +1823,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1442,14 +1887,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1487,7 +1928,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1593,7 +2034,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1735,7 +2176,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1746,7 +2187,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.375" style="1" bestFit="1" customWidth="1"/>
@@ -1755,27 +2196,1111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>80</v>
+      <c r="A1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07FAAE23-C83A-4CDC-B27A-0A83CD5912A4}">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="B3" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31855F33-B174-47D6-84D9-AA231F9E4634}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B37"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1638215-68AA-418A-84DB-BD777CC70393}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C3A426A-A8BC-4549-8B9B-693B6136A4FB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EDA54C-D4C6-4CDF-B8AF-4E1623A5C5A4}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.3">
@@ -1783,7 +3308,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.3">
@@ -1791,303 +3316,47 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>115</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>79</v>
+      <c r="A10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
